--- a/plate3d/PLATE3D_BCJOINT.xlsx
+++ b/plate3d/PLATE3D_BCJOINT.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="95">
   <si>
     <t># PLATE3D  ·  beam-to-column connection, written with SECT</t>
   </si>
@@ -112,22 +112,28 @@
     <t>[nut_h]</t>
   </si>
   <si>
+    <t>[proj]</t>
+  </si>
+  <si>
     <t>#   the point on the MODULE row is the underside of the head, so these start</t>
   </si>
   <si>
     <t>#   on the steel face and the head stands off behind it</t>
   </si>
   <si>
-    <t>#   length = grip + nut + proj. proj is the thread showing past the nut, and</t>
-  </si>
-  <si>
-    <t>#   written longer than that stands its nut off the steel - which is the right</t>
-  </si>
-  <si>
-    <t>#   way for a wrong length to show itself. Grip here is flange + cleat, and</t>
-  </si>
-  <si>
-    <t>#   cleat + web + cleat.</t>
+    <t>#   length = grip + nut + proj, and proj is the thread showing past the nut.</t>
+  </si>
+  <si>
+    <t>#   Grip is flange + cleat, 23, and cleat + web + cleat, 22.5. Bolts come in</t>
+  </si>
+  <si>
+    <t>#   catalogue lengths, so both are written 45 and proj takes up the rest -</t>
+  </si>
+  <si>
+    <t>#   7.6 and 8.1. Left blank proj would be 0.2d and the lengths would come out</t>
+  </si>
+  <si>
+    <t>#   40.6 and 40.1: two take-off lines for a bolt nobody orders twice.</t>
   </si>
   <si>
     <t>BOLT</t>
@@ -677,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:P55"/>
+  <dimension ref="B1:P56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -871,7 +877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
@@ -902,559 +908,573 @@
       <c r="K12" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="L12" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D19" t="s">
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E19">
-        <v>16</v>
-      </c>
-      <c r="F19">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20">
         <v>16</v>
       </c>
       <c r="F20">
-        <v>40.1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E21">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <v>45</v>
+      </c>
+      <c r="L21">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="N23" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>57</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D31" t="s">
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
         <v>19</v>
       </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>69</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C33" t="s">
         <v>68</v>
       </c>
-      <c r="E32" t="s">
+      <c r="D33" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" t="s">
         <v>19</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" t="s">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
         <v>23</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="E36" t="s">
         <v>23</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F36" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41">
+        <v>-45</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="H41">
+        <v>30</v>
+      </c>
+      <c r="I41" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>40</v>
+      </c>
+      <c r="P41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" t="s">
         <v>24</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="F42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C44" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>77</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
         <v>40</v>
       </c>
-      <c r="F40">
-        <v>-45</v>
-      </c>
-      <c r="G40">
-        <v>5</v>
-      </c>
-      <c r="H40">
-        <v>30</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="P44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" t="s">
         <v>70</v>
       </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>40</v>
-      </c>
-      <c r="P40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" t="s">
-        <v>68</v>
-      </c>
-      <c r="E41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E45" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43" t="s">
-        <v>75</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>40</v>
-      </c>
-      <c r="P43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" t="s">
-        <v>68</v>
-      </c>
-      <c r="E44" t="s">
-        <v>76</v>
-      </c>
-      <c r="F44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="1" t="s">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+      <c r="H47" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C47" t="s">
+      <c r="I47" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D47" t="s">
-        <v>66</v>
-      </c>
-      <c r="E47" t="s">
-        <v>86</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>-800</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F48">
+      <c r="C49" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49">
         <v>160</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>87</v>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" t="s">
-        <v>89</v>
-      </c>
-      <c r="D51" t="s">
-        <v>73</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="F52">
+        <v>180</v>
+      </c>
+      <c r="G52">
+        <v>33.25</v>
+      </c>
+      <c r="H52">
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F51">
-        <v>180</v>
-      </c>
-      <c r="G51">
-        <v>33.25</v>
-      </c>
-      <c r="H51">
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" t="s">
-        <v>89</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="C53" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" t="s">
         <v>91</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" t="s">
-        <v>85</v>
-      </c>
-      <c r="D53" t="s">
-        <v>74</v>
-      </c>
       <c r="E53" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F53">
+      <c r="C54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54">
         <v>185</v>
       </c>
-      <c r="G53">
+      <c r="G54">
         <v>11.25</v>
       </c>
-      <c r="H53">
+      <c r="H54">
         <v>-40</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
-        <v>92</v>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_BCJOINT.xlsx
+++ b/plate3d/PLATE3D_BCJOINT.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="226">
   <si>
     <t>BEAM TO COLUMN</t>
   </si>
@@ -341,6 +341,30 @@
   </si>
   <si>
     <t>MIR</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>BCJOINT - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -1712,13 +1736,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -1727,12 +1751,12 @@
     <col min="4" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>63</v>
       </c>
@@ -1740,12 +1764,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>66</v>
       </c>
@@ -1905,17 +1929,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>78</v>
       </c>
@@ -1996,17 +2020,17 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>85</v>
       </c>
@@ -2047,7 +2071,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>87</v>
       </c>
@@ -2064,12 +2088,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>87</v>
       </c>
@@ -2093,7 +2117,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>87</v>
       </c>
@@ -2110,7 +2134,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>65</v>
       </c>
@@ -2195,7 +2219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
         <v>87</v>
       </c>
@@ -2212,12 +2236,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
         <v>87</v>
       </c>
@@ -2264,7 +2288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>87</v>
       </c>
@@ -2281,17 +2305,17 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B30" s="14" t="s">
         <v>100</v>
       </c>
@@ -2400,7 +2424,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B34" s="14" t="s">
         <v>100</v>
       </c>
@@ -2426,19 +2450,70 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="14" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36">
+        <v>50</v>
+      </c>
+      <c r="H36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38">
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="14" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2475,7 +2550,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B2" s="19">
         <v>100</v>
@@ -2498,7 +2573,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B3" s="21">
         <v>125</v>
@@ -2521,7 +2596,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B4" s="19">
         <v>150</v>
@@ -2544,7 +2619,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B5" s="21">
         <v>148</v>
@@ -2567,7 +2642,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B6" s="19">
         <v>150</v>
@@ -2590,7 +2665,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B7" s="21">
         <v>198</v>
@@ -2613,7 +2688,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B8" s="19">
         <v>200</v>
@@ -2636,7 +2711,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B9" s="21">
         <v>194</v>
@@ -2659,7 +2734,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B10" s="19">
         <v>200</v>
@@ -2682,7 +2757,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B11" s="21">
         <v>200</v>
@@ -2705,7 +2780,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B12" s="19">
         <v>248</v>
@@ -2728,7 +2803,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B13" s="21">
         <v>250</v>
@@ -2751,7 +2826,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B14" s="19">
         <v>244</v>
@@ -2774,7 +2849,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B15" s="21">
         <v>250</v>
@@ -2797,7 +2872,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B16" s="19">
         <v>250</v>
@@ -2820,7 +2895,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B17" s="21">
         <v>298</v>
@@ -2866,7 +2941,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B19" s="21">
         <v>294</v>
@@ -2889,7 +2964,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B20" s="19">
         <v>294</v>
@@ -2935,7 +3010,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B22" s="19">
         <v>300</v>
@@ -2958,7 +3033,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B23" s="21">
         <v>346</v>
@@ -2981,7 +3056,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B24" s="19">
         <v>350</v>
@@ -3004,7 +3079,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B25" s="21">
         <v>340</v>
@@ -3027,7 +3102,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B26" s="19">
         <v>344</v>
@@ -3050,7 +3125,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B27" s="21">
         <v>350</v>
@@ -3073,7 +3148,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B28" s="19">
         <v>396</v>
@@ -3096,7 +3171,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B29" s="21">
         <v>400</v>
@@ -3119,7 +3194,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B30" s="19">
         <v>390</v>
@@ -3142,7 +3217,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B31" s="21">
         <v>388</v>
@@ -3165,7 +3240,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B32" s="19">
         <v>394</v>
@@ -3188,7 +3263,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B33" s="21">
         <v>400</v>
@@ -3211,7 +3286,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B34" s="19">
         <v>400</v>
@@ -3234,7 +3309,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B35" s="21">
         <v>414</v>
@@ -3257,7 +3332,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B36" s="19">
         <v>428</v>
@@ -3280,7 +3355,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B37" s="21">
         <v>458</v>
@@ -3303,7 +3378,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B38" s="19">
         <v>498</v>
@@ -3326,7 +3401,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B39" s="21">
         <v>446</v>
@@ -3349,7 +3424,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B40" s="19">
         <v>450</v>
@@ -3372,7 +3447,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B41" s="21">
         <v>440</v>
@@ -3395,7 +3470,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B42" s="19">
         <v>440</v>
@@ -3418,7 +3493,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B43" s="21">
         <v>496</v>
@@ -3441,7 +3516,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B44" s="19">
         <v>500</v>
@@ -3464,7 +3539,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B45" s="21">
         <v>482</v>
@@ -3487,7 +3562,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B46" s="19">
         <v>488</v>
@@ -3510,7 +3585,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B47" s="21">
         <v>596</v>
@@ -3533,7 +3608,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B48" s="19">
         <v>600</v>
@@ -3556,7 +3631,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B49" s="21">
         <v>582</v>
@@ -3579,7 +3654,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B50" s="19">
         <v>588</v>
@@ -3602,7 +3677,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B51" s="21">
         <v>594</v>
@@ -3625,7 +3700,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B52" s="19">
         <v>692</v>
@@ -3648,7 +3723,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B53" s="21">
         <v>700</v>
@@ -3671,7 +3746,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B54" s="19">
         <v>792</v>
@@ -3694,7 +3769,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B55" s="21">
         <v>800</v>
@@ -3717,7 +3792,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B56" s="19">
         <v>890</v>
@@ -3740,7 +3815,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B57" s="21">
         <v>900</v>
@@ -3763,7 +3838,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B58" s="19">
         <v>912</v>
@@ -3786,7 +3861,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B59" s="21">
         <v>918</v>
@@ -3809,7 +3884,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3846,7 +3921,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B2" s="19">
         <v>25</v>
@@ -3869,7 +3944,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B3" s="21">
         <v>30</v>
@@ -3892,7 +3967,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B4" s="19">
         <v>40</v>
@@ -3915,7 +3990,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B5" s="21">
         <v>40</v>
@@ -3938,7 +4013,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B6" s="19">
         <v>45</v>
@@ -3961,7 +4036,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B7" s="21">
         <v>45</v>
@@ -3984,7 +4059,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B8" s="19">
         <v>50</v>
@@ -4007,7 +4082,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B9" s="21">
         <v>50</v>
@@ -4030,7 +4105,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B10" s="19">
         <v>50</v>
@@ -4053,7 +4128,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B11" s="21">
         <v>60</v>
@@ -4076,7 +4151,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B12" s="19">
         <v>60</v>
@@ -4099,7 +4174,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B13" s="21">
         <v>65</v>
@@ -4122,7 +4197,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B14" s="19">
         <v>65</v>
@@ -4168,7 +4243,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B16" s="19">
         <v>70</v>
@@ -4191,7 +4266,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B17" s="21">
         <v>75</v>
@@ -4214,7 +4289,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B18" s="19">
         <v>75</v>
@@ -4237,7 +4312,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B19" s="21">
         <v>75</v>
@@ -4260,7 +4335,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B20" s="19">
         <v>80</v>
@@ -4283,7 +4358,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B21" s="21">
         <v>90</v>
@@ -4306,7 +4381,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B22" s="19">
         <v>90</v>
@@ -4329,7 +4404,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B23" s="21">
         <v>90</v>
@@ -4352,7 +4427,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B24" s="19">
         <v>90</v>
@@ -4375,7 +4450,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B25" s="21">
         <v>100</v>
@@ -4398,7 +4473,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B26" s="19">
         <v>100</v>
@@ -4421,7 +4496,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B27" s="21">
         <v>100</v>
@@ -4444,7 +4519,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B28" s="19">
         <v>120</v>
@@ -4467,7 +4542,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B29" s="21">
         <v>130</v>
@@ -4490,7 +4565,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B30" s="19">
         <v>130</v>
@@ -4513,7 +4588,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B31" s="21">
         <v>130</v>
@@ -4536,7 +4611,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B32" s="19">
         <v>150</v>
@@ -4559,7 +4634,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B33" s="21">
         <v>150</v>
@@ -4582,7 +4657,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B34" s="19">
         <v>150</v>
@@ -4605,7 +4680,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B35" s="21">
         <v>175</v>
@@ -4628,7 +4703,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B36" s="19">
         <v>175</v>
@@ -4651,7 +4726,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B37" s="21">
         <v>200</v>
@@ -4674,7 +4749,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B38" s="19">
         <v>200</v>
@@ -4697,7 +4772,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B39" s="21">
         <v>200</v>
@@ -4720,7 +4795,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B40" s="19">
         <v>250</v>
@@ -4743,7 +4818,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B41" s="21">
         <v>250</v>
@@ -4766,7 +4841,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B42" s="19">
         <v>50</v>
@@ -4789,7 +4864,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B43" s="21">
         <v>90</v>
@@ -4812,7 +4887,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B44" s="19">
         <v>100</v>
@@ -4835,7 +4910,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B45" s="21">
         <v>100</v>
@@ -4858,7 +4933,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B46" s="19">
         <v>125</v>
@@ -4881,7 +4956,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B47" s="21">
         <v>125</v>
@@ -4904,7 +4979,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B48" s="19">
         <v>125</v>
@@ -4927,7 +5002,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B49" s="21">
         <v>125</v>
@@ -4950,7 +5025,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B50" s="19">
         <v>150</v>
@@ -4973,7 +5048,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B51" s="21">
         <v>150</v>
@@ -4996,7 +5071,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B52" s="19">
         <v>150</v>
@@ -5019,7 +5094,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B53" s="21">
         <v>150</v>
@@ -5042,7 +5117,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B54" s="19">
         <v>150</v>
@@ -5065,6 +5140,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_BCJOINT.xlsx
+++ b/plate3d/PLATE3D_BCJOINT.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="218">
   <si>
     <t>BEAM TO COLUMN</t>
   </si>
@@ -341,30 +341,6 @@
   </si>
   <si>
     <t>MIR</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>BCJOINT - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -1736,13 +1712,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -1751,12 +1727,12 @@
     <col min="4" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>63</v>
       </c>
@@ -1764,12 +1740,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>66</v>
       </c>
@@ -1929,17 +1905,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>78</v>
       </c>
@@ -2020,17 +1996,17 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>85</v>
       </c>
@@ -2071,7 +2047,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>87</v>
       </c>
@@ -2088,12 +2064,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>87</v>
       </c>
@@ -2117,7 +2093,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>87</v>
       </c>
@@ -2134,7 +2110,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>65</v>
       </c>
@@ -2219,7 +2195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
         <v>87</v>
       </c>
@@ -2236,12 +2212,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
         <v>87</v>
       </c>
@@ -2288,7 +2264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>87</v>
       </c>
@@ -2305,17 +2281,17 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="14" t="s">
         <v>100</v>
       </c>
@@ -2424,7 +2400,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="14" t="s">
         <v>100</v>
       </c>
@@ -2450,70 +2426,19 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" t="s">
-        <v>110</v>
-      </c>
-      <c r="G36">
-        <v>50</v>
-      </c>
-      <c r="H36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38">
-        <v>20</v>
-      </c>
-      <c r="F38" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="14" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -2550,7 +2475,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B2" s="19">
         <v>100</v>
@@ -2573,7 +2498,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B3" s="21">
         <v>125</v>
@@ -2596,7 +2521,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B4" s="19">
         <v>150</v>
@@ -2619,7 +2544,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B5" s="21">
         <v>148</v>
@@ -2642,7 +2567,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B6" s="19">
         <v>150</v>
@@ -2665,7 +2590,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B7" s="21">
         <v>198</v>
@@ -2688,7 +2613,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B8" s="19">
         <v>200</v>
@@ -2711,7 +2636,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B9" s="21">
         <v>194</v>
@@ -2734,7 +2659,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B10" s="19">
         <v>200</v>
@@ -2757,7 +2682,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B11" s="21">
         <v>200</v>
@@ -2780,7 +2705,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B12" s="19">
         <v>248</v>
@@ -2803,7 +2728,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B13" s="21">
         <v>250</v>
@@ -2826,7 +2751,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B14" s="19">
         <v>244</v>
@@ -2849,7 +2774,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B15" s="21">
         <v>250</v>
@@ -2872,7 +2797,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B16" s="19">
         <v>250</v>
@@ -2895,7 +2820,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B17" s="21">
         <v>298</v>
@@ -2941,7 +2866,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B19" s="21">
         <v>294</v>
@@ -2964,7 +2889,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B20" s="19">
         <v>294</v>
@@ -3010,7 +2935,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B22" s="19">
         <v>300</v>
@@ -3033,7 +2958,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B23" s="21">
         <v>346</v>
@@ -3056,7 +2981,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B24" s="19">
         <v>350</v>
@@ -3079,7 +3004,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B25" s="21">
         <v>340</v>
@@ -3102,7 +3027,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B26" s="19">
         <v>344</v>
@@ -3125,7 +3050,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B27" s="21">
         <v>350</v>
@@ -3148,7 +3073,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B28" s="19">
         <v>396</v>
@@ -3171,7 +3096,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B29" s="21">
         <v>400</v>
@@ -3194,7 +3119,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B30" s="19">
         <v>390</v>
@@ -3217,7 +3142,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B31" s="21">
         <v>388</v>
@@ -3240,7 +3165,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B32" s="19">
         <v>394</v>
@@ -3263,7 +3188,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B33" s="21">
         <v>400</v>
@@ -3286,7 +3211,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B34" s="19">
         <v>400</v>
@@ -3309,7 +3234,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B35" s="21">
         <v>414</v>
@@ -3332,7 +3257,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B36" s="19">
         <v>428</v>
@@ -3355,7 +3280,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B37" s="21">
         <v>458</v>
@@ -3378,7 +3303,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B38" s="19">
         <v>498</v>
@@ -3401,7 +3326,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B39" s="21">
         <v>446</v>
@@ -3424,7 +3349,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B40" s="19">
         <v>450</v>
@@ -3447,7 +3372,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B41" s="21">
         <v>440</v>
@@ -3470,7 +3395,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B42" s="19">
         <v>440</v>
@@ -3493,7 +3418,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B43" s="21">
         <v>496</v>
@@ -3516,7 +3441,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B44" s="19">
         <v>500</v>
@@ -3539,7 +3464,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B45" s="21">
         <v>482</v>
@@ -3562,7 +3487,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B46" s="19">
         <v>488</v>
@@ -3585,7 +3510,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B47" s="21">
         <v>596</v>
@@ -3608,7 +3533,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B48" s="19">
         <v>600</v>
@@ -3631,7 +3556,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B49" s="21">
         <v>582</v>
@@ -3654,7 +3579,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B50" s="19">
         <v>588</v>
@@ -3677,7 +3602,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B51" s="21">
         <v>594</v>
@@ -3700,7 +3625,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B52" s="19">
         <v>692</v>
@@ -3723,7 +3648,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B53" s="21">
         <v>700</v>
@@ -3746,7 +3671,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B54" s="19">
         <v>792</v>
@@ -3769,7 +3694,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B55" s="21">
         <v>800</v>
@@ -3792,7 +3717,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B56" s="19">
         <v>890</v>
@@ -3815,7 +3740,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B57" s="21">
         <v>900</v>
@@ -3838,7 +3763,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B58" s="19">
         <v>912</v>
@@ -3861,7 +3786,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B59" s="21">
         <v>918</v>
@@ -3884,7 +3809,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -3921,7 +3846,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B2" s="19">
         <v>25</v>
@@ -3944,7 +3869,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B3" s="21">
         <v>30</v>
@@ -3967,7 +3892,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B4" s="19">
         <v>40</v>
@@ -3990,7 +3915,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B5" s="21">
         <v>40</v>
@@ -4013,7 +3938,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B6" s="19">
         <v>45</v>
@@ -4036,7 +3961,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B7" s="21">
         <v>45</v>
@@ -4059,7 +3984,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B8" s="19">
         <v>50</v>
@@ -4082,7 +4007,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B9" s="21">
         <v>50</v>
@@ -4105,7 +4030,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B10" s="19">
         <v>50</v>
@@ -4128,7 +4053,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B11" s="21">
         <v>60</v>
@@ -4151,7 +4076,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B12" s="19">
         <v>60</v>
@@ -4174,7 +4099,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B13" s="21">
         <v>65</v>
@@ -4197,7 +4122,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B14" s="19">
         <v>65</v>
@@ -4243,7 +4168,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B16" s="19">
         <v>70</v>
@@ -4266,7 +4191,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B17" s="21">
         <v>75</v>
@@ -4289,7 +4214,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B18" s="19">
         <v>75</v>
@@ -4312,7 +4237,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B19" s="21">
         <v>75</v>
@@ -4335,7 +4260,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B20" s="19">
         <v>80</v>
@@ -4358,7 +4283,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B21" s="21">
         <v>90</v>
@@ -4381,7 +4306,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B22" s="19">
         <v>90</v>
@@ -4404,7 +4329,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B23" s="21">
         <v>90</v>
@@ -4427,7 +4352,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B24" s="19">
         <v>90</v>
@@ -4450,7 +4375,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B25" s="21">
         <v>100</v>
@@ -4473,7 +4398,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B26" s="19">
         <v>100</v>
@@ -4496,7 +4421,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B27" s="21">
         <v>100</v>
@@ -4519,7 +4444,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B28" s="19">
         <v>120</v>
@@ -4542,7 +4467,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B29" s="21">
         <v>130</v>
@@ -4565,7 +4490,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B30" s="19">
         <v>130</v>
@@ -4588,7 +4513,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B31" s="21">
         <v>130</v>
@@ -4611,7 +4536,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B32" s="19">
         <v>150</v>
@@ -4634,7 +4559,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B33" s="21">
         <v>150</v>
@@ -4657,7 +4582,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B34" s="19">
         <v>150</v>
@@ -4680,7 +4605,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B35" s="21">
         <v>175</v>
@@ -4703,7 +4628,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B36" s="19">
         <v>175</v>
@@ -4726,7 +4651,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B37" s="21">
         <v>200</v>
@@ -4749,7 +4674,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B38" s="19">
         <v>200</v>
@@ -4772,7 +4697,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B39" s="21">
         <v>200</v>
@@ -4795,7 +4720,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B40" s="19">
         <v>250</v>
@@ -4818,7 +4743,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B41" s="21">
         <v>250</v>
@@ -4841,7 +4766,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B42" s="19">
         <v>50</v>
@@ -4864,7 +4789,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B43" s="21">
         <v>90</v>
@@ -4887,7 +4812,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B44" s="19">
         <v>100</v>
@@ -4910,7 +4835,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B45" s="21">
         <v>100</v>
@@ -4933,7 +4858,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B46" s="19">
         <v>125</v>
@@ -4956,7 +4881,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B47" s="21">
         <v>125</v>
@@ -4979,7 +4904,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B48" s="19">
         <v>125</v>
@@ -5002,7 +4927,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B49" s="21">
         <v>125</v>
@@ -5025,7 +4950,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B50" s="19">
         <v>150</v>
@@ -5048,7 +4973,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B51" s="21">
         <v>150</v>
@@ -5071,7 +4996,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B52" s="19">
         <v>150</v>
@@ -5094,7 +5019,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B53" s="21">
         <v>150</v>
@@ -5117,7 +5042,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B54" s="19">
         <v>150</v>
@@ -5140,6 +5065,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>